--- a/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71715585-32E8-4BCA-B111-D1D9AF3F4D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DF62FD-FC4C-42B1-8623-41B74E892A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -461,6 +461,24 @@
         <v>0.4秒後,-1秒間の間, 0.05秒間毎に</v>
       </c>
     </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="str">
+        <f>D5&amp;"秒後,"&amp;B5&amp;"秒間の間, "&amp;C5&amp;"秒間毎に"</f>
+        <v>0秒後,5秒間の間, 0.5秒間毎に</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DF62FD-FC4C-42B1-8623-41B74E892A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D8E8FB-2B7B-426C-B555-22ED209E5B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3720" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2970" yWindow="-13125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -387,7 +387,7 @@
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionIntervalParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D8E8FB-2B7B-426C-B555-22ED209E5B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0C3AB1-8435-4C83-87A9-9C15937AB9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="-13125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2805" yWindow="1605" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -381,13 +381,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -395,13 +395,13 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -412,17 +412,17 @@
         <v>0</v>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.3</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2" t="str">
-        <f>D2&amp;"秒後,"&amp;B2&amp;"秒間の間, "&amp;C2&amp;"秒間毎に"</f>
-        <v>0秒後,3秒間の間, 0.3秒間毎に</v>
+        <f>IF(B2&gt;0,"開始後"&amp;B2&amp;"秒経過した後に","開始直後に")&amp;" , "&amp;IF(C2&gt;0,C2&amp;"秒間の間","永続的に")&amp;"  , "&amp;IF(D2&gt;0,D2&amp;"秒間毎に","毎フレーム")</f>
+        <v>開始直後に , 3秒間の間  , 0.3秒間毎に</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -430,17 +430,17 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3" t="str">
-        <f>D3&amp;"秒後,"&amp;B3&amp;"秒間の間, "&amp;C3&amp;"秒間毎に"</f>
-        <v>0秒後,3秒間の間, 0.5秒間毎に</v>
+        <f t="shared" ref="E3:E6" si="0">IF(B3&gt;0,"開始後"&amp;B3&amp;"秒経過した後に","開始直後に")&amp;" , "&amp;IF(C3&gt;0,C3&amp;"秒間の間","永続的に")&amp;"  , "&amp;IF(D3&gt;0,D3&amp;"秒間毎に","毎フレーム")</f>
+        <v>開始直後に , 3秒間の間  , 0.5秒間毎に</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -448,17 +448,17 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>0.4</v>
+      </c>
+      <c r="C4">
         <v>-1</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.05</v>
       </c>
-      <c r="D4">
-        <v>0.4</v>
-      </c>
       <c r="E4" t="str">
-        <f>D4&amp;"秒後,"&amp;B4&amp;"秒間の間, "&amp;C4&amp;"秒間毎に"</f>
-        <v>0.4秒後,-1秒間の間, 0.05秒間毎に</v>
+        <f t="shared" si="0"/>
+        <v>開始後0.4秒経過した後に , 永続的に  , 0.05秒間毎に</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -466,17 +466,35 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>5</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.5</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5" t="str">
-        <f>D5&amp;"秒後,"&amp;B5&amp;"秒間の間, "&amp;C5&amp;"秒間毎に"</f>
-        <v>0秒後,5秒間の間, 0.5秒間毎に</v>
+        <f t="shared" si="0"/>
+        <v>開始直後に , 5秒間の間  , 0.5秒間毎に</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>-1</v>
+      </c>
+      <c r="D6">
+        <v>-5</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>開始後5秒経過した後に , 永続的に  , 毎フレーム</v>
       </c>
     </row>
   </sheetData>
